--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R2" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,49 +768,64 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R3" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,6 +885,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -2145,6 +2165,16 @@
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ella-Paulina Åhrén</t>
+        </is>
+      </c>
       <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R2" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>92628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R3" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>127776001</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127776692</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127776780</v>
       </c>
       <c r="B3" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127776518</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>127775718</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>127775221</v>
       </c>
       <c r="B11" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>127776001</v>
       </c>
       <c r="B12" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>127775846</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127776692</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>127776780</v>
       </c>
       <c r="B3" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127776518</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>127775718</v>
       </c>
       <c r="B6" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127775221</v>
+        <v>127776001</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>92667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567931</v>
+        <v>567861</v>
       </c>
       <c r="R11" t="n">
-        <v>7084859</v>
+        <v>7084831</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,19 +1732,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127776001</v>
+        <v>127775221</v>
       </c>
       <c r="B12" t="n">
-        <v>92659</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567861</v>
+        <v>567931</v>
       </c>
       <c r="R12" t="n">
-        <v>7084831</v>
+        <v>7084859</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,9 +1829,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,12 +1856,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
         <v>127775846</v>
       </c>
       <c r="B13" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R2" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B3" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R3" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>127776001</v>
       </c>
       <c r="B11" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R2" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R3" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127776001</v>
+        <v>127775221</v>
       </c>
       <c r="B11" t="n">
-        <v>92668</v>
+        <v>78787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567861</v>
+        <v>567931</v>
       </c>
       <c r="R11" t="n">
-        <v>7084831</v>
+        <v>7084859</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,9 +1732,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1759,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127775221</v>
+        <v>127776001</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>92669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567931</v>
+        <v>567861</v>
       </c>
       <c r="R12" t="n">
-        <v>7084859</v>
+        <v>7084831</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,19 +1839,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,12 +1856,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R2" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B3" t="n">
-        <v>92641</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R3" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127775221</v>
+        <v>127776001</v>
       </c>
       <c r="B11" t="n">
-        <v>78787</v>
+        <v>92670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567931</v>
+        <v>567861</v>
       </c>
       <c r="R11" t="n">
-        <v>7084859</v>
+        <v>7084831</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,19 +1732,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127776001</v>
+        <v>127775221</v>
       </c>
       <c r="B12" t="n">
-        <v>92669</v>
+        <v>78787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567861</v>
+        <v>567931</v>
       </c>
       <c r="R12" t="n">
-        <v>7084831</v>
+        <v>7084859</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,9 +1829,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,12 +1856,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R2" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R3" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127776001</v>
+        <v>127775221</v>
       </c>
       <c r="B11" t="n">
-        <v>92670</v>
+        <v>78787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567861</v>
+        <v>567931</v>
       </c>
       <c r="R11" t="n">
-        <v>7084831</v>
+        <v>7084859</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,9 +1732,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1759,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127775221</v>
+        <v>127776001</v>
       </c>
       <c r="B12" t="n">
-        <v>78787</v>
+        <v>92670</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567931</v>
+        <v>567861</v>
       </c>
       <c r="R12" t="n">
-        <v>7084859</v>
+        <v>7084831</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,19 +1839,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,12 +1856,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R2" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B3" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R3" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R2" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R3" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R2" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R3" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127776518</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>127775718</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127775221</v>
+        <v>127776001</v>
       </c>
       <c r="B11" t="n">
-        <v>78787</v>
+        <v>92678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567931</v>
+        <v>567861</v>
       </c>
       <c r="R11" t="n">
-        <v>7084859</v>
+        <v>7084831</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,19 +1732,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127776001</v>
+        <v>127775221</v>
       </c>
       <c r="B12" t="n">
-        <v>92670</v>
+        <v>78790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567861</v>
+        <v>567931</v>
       </c>
       <c r="R12" t="n">
-        <v>7084831</v>
+        <v>7084859</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,9 +1829,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,12 +1856,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
         <v>127775846</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127776001</v>
+        <v>127775221</v>
       </c>
       <c r="B11" t="n">
-        <v>92678</v>
+        <v>78790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567861</v>
+        <v>567931</v>
       </c>
       <c r="R11" t="n">
-        <v>7084831</v>
+        <v>7084859</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,9 +1732,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1759,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127775221</v>
+        <v>127776001</v>
       </c>
       <c r="B12" t="n">
-        <v>78790</v>
+        <v>92678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567931</v>
+        <v>567861</v>
       </c>
       <c r="R12" t="n">
-        <v>7084859</v>
+        <v>7084831</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,19 +1839,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,12 +1856,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776692</v>
+        <v>127776780</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567935</v>
+        <v>567922</v>
       </c>
       <c r="R2" t="n">
-        <v>7084834</v>
+        <v>7084833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776780</v>
+        <v>127776692</v>
       </c>
       <c r="B3" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567922</v>
+        <v>567935</v>
       </c>
       <c r="R3" t="n">
-        <v>7084833</v>
+        <v>7084834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>127776971</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127776518</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>127775718</v>
       </c>
       <c r="B6" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>127774723</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>127774278</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127775069</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127775120</v>
       </c>
       <c r="B10" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127775221</v>
+        <v>127776001</v>
       </c>
       <c r="B11" t="n">
-        <v>78790</v>
+        <v>92770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567931</v>
+        <v>567861</v>
       </c>
       <c r="R11" t="n">
-        <v>7084859</v>
+        <v>7084831</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,19 +1732,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127776001</v>
+        <v>127775221</v>
       </c>
       <c r="B12" t="n">
-        <v>92678</v>
+        <v>78840</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567861</v>
+        <v>567931</v>
       </c>
       <c r="R12" t="n">
-        <v>7084831</v>
+        <v>7084859</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,9 +1829,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,12 +1856,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
         <v>127775846</v>
       </c>
       <c r="B13" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>127775842</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>127776430</v>
       </c>
       <c r="B15" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127776780</v>
+        <v>127775708</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567922</v>
+        <v>567860</v>
       </c>
       <c r="R2" t="n">
-        <v>7084833</v>
+        <v>7084886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127776692</v>
+        <v>127775120</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567935</v>
+        <v>567931</v>
       </c>
       <c r="R3" t="n">
-        <v>7084834</v>
+        <v>7084867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,69 +877,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ella-Paulina Åhrén</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127776971</v>
+        <v>127775842</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567962</v>
+        <v>567861</v>
       </c>
       <c r="R4" t="n">
-        <v>7084778</v>
+        <v>7084831</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +957,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127776518</v>
+        <v>127776430</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,42 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567922</v>
+        <v>567914</v>
       </c>
       <c r="R5" t="n">
-        <v>7084830</v>
+        <v>7084828</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127775718</v>
+        <v>127776780</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567890</v>
+        <v>567922</v>
       </c>
       <c r="R6" t="n">
-        <v>7084855</v>
+        <v>7084833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,69 +1188,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127774723</v>
+        <v>127775305</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567958</v>
+        <v>567912</v>
       </c>
       <c r="R7" t="n">
-        <v>7084872</v>
+        <v>7084890</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,9 +1268,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,69 +1295,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127774278</v>
+        <v>127775221</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567964</v>
+        <v>567931</v>
       </c>
       <c r="R8" t="n">
-        <v>7084885</v>
+        <v>7084859</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,9 +1375,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,66 +1402,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127775069</v>
+        <v>127777215</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567949</v>
+        <v>568021</v>
       </c>
       <c r="R9" t="n">
-        <v>7084881</v>
+        <v>7084739</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1528,9 +1482,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,60 +1509,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127775120</v>
+        <v>127774875</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567931</v>
+        <v>567939</v>
       </c>
       <c r="R10" t="n">
-        <v>7084867</v>
+        <v>7084890</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1625,19 +1594,14 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:29</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,22 +1616,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127776001</v>
+        <v>127774904</v>
       </c>
       <c r="B11" t="n">
-        <v>92770</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,37 +1639,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567861</v>
+        <v>567938</v>
       </c>
       <c r="R11" t="n">
-        <v>7084831</v>
+        <v>7084892</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1732,9 +1701,24 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127775221</v>
+        <v>127776518</v>
       </c>
       <c r="B12" t="n">
-        <v>78840</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,34 +1756,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567931</v>
+        <v>567922</v>
       </c>
       <c r="R12" t="n">
-        <v>7084859</v>
+        <v>7084830</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1841,7 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127775846</v>
+        <v>127776692</v>
       </c>
       <c r="B13" t="n">
-        <v>78841</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567871</v>
+        <v>567935</v>
       </c>
       <c r="R13" t="n">
-        <v>7084842</v>
+        <v>7084834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1948,7 +1947,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,22 +1967,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127775842</v>
+        <v>127775383</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2010,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567861</v>
+        <v>567906</v>
       </c>
       <c r="R14" t="n">
-        <v>7084831</v>
+        <v>7084891</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2043,9 +2047,19 @@
           <t>2025-08-24</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,60 +2074,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127776430</v>
+        <v>127774278</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567914</v>
+        <v>567964</v>
       </c>
       <c r="R15" t="n">
-        <v>7084828</v>
+        <v>7084885</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,19 +2163,9 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,15 +2180,1003 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127774723</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567958</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7084872</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127775069</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567949</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7084881</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127776971</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567962</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7084778</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127777006</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567977</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7084799</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Ella-Paulina Åhrén</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127774340</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567969</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7084911</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127777166</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>568005</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7084751</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127774579</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567972</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7084896</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127775718</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567890</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7084855</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127775846</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Grubbmyrlokarna, Grubbmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567871</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7084842</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52582-2024 artfynd.xlsx
+++ b/artfynd/A 52582-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775708</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775305</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775221</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774875</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774904</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776518</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776692</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775383</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774278</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2295,6 +2370,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774723</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2401,6 +2481,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775069</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2517,6 +2602,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127776971</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2633,6 +2723,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777006</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2740,6 +2835,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774340</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2856,6 +2956,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127777166</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2963,6 +3068,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127774579</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3070,6 +3180,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775718</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3177,8 +3292,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127775846</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>